--- a/data/trans_orig/IP24_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15324</t>
+          <t>15852</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19688</t>
+          <t>19127</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>17402</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30710</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37244</t>
+          <t>36716</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46383</t>
+          <t>45682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40529</t>
+          <t>41090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>51641</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82075</t>
+          <t>81119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95759</t>
+          <t>95383</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30093</t>
+          <t>29679</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9097</t>
+          <t>9682</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20754</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28712</t>
+          <t>28449</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45026</t>
+          <t>46296</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70837</t>
+          <t>71251</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84759</t>
+          <t>84124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88003</t>
+          <t>88718</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99660</t>
+          <t>99075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164661</t>
+          <t>163391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180975</t>
+          <t>181238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,43%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14664</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26473</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19713</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26057</t>
+          <t>27283</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43631</t>
+          <t>43977</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39670</t>
+          <t>38984</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51479</t>
+          <t>52164</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50614</t>
+          <t>50264</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60387</t>
+          <t>60886</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>92839</t>
+          <t>92493</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110413</t>
+          <t>109187</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20704</t>
+          <t>20380</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>20050</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21016</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36489</t>
+          <t>36195</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54157</t>
+          <t>54481</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65493</t>
+          <t>66367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58838</t>
+          <t>59061</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70149</t>
+          <t>69923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117483</t>
+          <t>117777</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132956</t>
+          <t>132961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14315</t>
+          <t>14086</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24428</t>
+          <t>24314</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23548</t>
+          <t>23394</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29323</t>
+          <t>30388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45127</t>
+          <t>45144</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,07%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27537</t>
+          <t>27766</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21295</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32131</t>
+          <t>32186</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41568</t>
+          <t>41551</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57372</t>
+          <t>56307</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>64,95%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19017</t>
+          <t>18409</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9071</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19282</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19868</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34532</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37038</t>
+          <t>37646</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47202</t>
+          <t>47956</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40450</t>
+          <t>40365</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50661</t>
+          <t>50430</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81255</t>
+          <t>81096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95919</t>
+          <t>95582</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,55%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25393</t>
+          <t>25413</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41358</t>
+          <t>42570</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34145</t>
+          <t>33850</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51227</t>
+          <t>51140</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63121</t>
+          <t>63543</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87245</t>
+          <t>88883</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>87264</t>
+          <t>86052</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103229</t>
+          <t>103209</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>83778</t>
+          <t>83865</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>100860</t>
+          <t>101155</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>176382</t>
+          <t>174744</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>200506</t>
+          <t>200084</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,9%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30450</t>
+          <t>30933</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47509</t>
+          <t>48752</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30194</t>
+          <t>30659</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46976</t>
+          <t>47570</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>66354</t>
+          <t>66386</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>90351</t>
+          <t>91175</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>110395</t>
+          <t>109152</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>127454</t>
+          <t>126971</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>116381</t>
+          <t>115787</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>133163</t>
+          <t>132698</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>230910</t>
+          <t>230086</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>254907</t>
+          <t>254875</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>153497</t>
+          <t>154519</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>189808</t>
+          <t>189953</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>151063</t>
+          <t>150375</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>188270</t>
+          <t>187450</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>313924</t>
+          <t>314300</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>366474</t>
+          <t>366319</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>489127</t>
+          <t>488982</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>525438</t>
+          <t>524416</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>533078</t>
+          <t>533898</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>570285</t>
+          <t>570973</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1033809</t>
+          <t>1033964</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1086359</t>
+          <t>1085983</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9604</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20431</t>
+          <t>22223</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20782</t>
+          <t>20527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>21101</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37215</t>
+          <t>37200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36027</t>
+          <t>34235</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46854</t>
+          <t>46002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42579</t>
+          <t>42834</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54053</t>
+          <t>54228</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82604</t>
+          <t>82619</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98904</t>
+          <t>98718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14128</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26725</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26269</t>
+          <t>26959</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30374</t>
+          <t>30651</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49461</t>
+          <t>49264</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77106</t>
+          <t>77266</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89703</t>
+          <t>90056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84262</t>
+          <t>83572</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97619</t>
+          <t>97225</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164901</t>
+          <t>165098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183988</t>
+          <t>183711</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,7%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17644</t>
+          <t>17327</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>16974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30282</t>
+          <t>29667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50534</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60936</t>
+          <t>61093</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54602</t>
+          <t>54280</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64423</t>
+          <t>64412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109150</t>
+          <t>109765</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123844</t>
+          <t>123808</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>15571</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>8797</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22449</t>
+          <t>22609</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60855</t>
+          <t>61141</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70225</t>
+          <t>70698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71153</t>
+          <t>71975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78301</t>
+          <t>78510</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135036</t>
+          <t>134876</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147561</t>
+          <t>147305</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11472</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21320</t>
+          <t>21018</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31639</t>
+          <t>31379</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39901</t>
+          <t>39881</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35280</t>
+          <t>35253</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43379</t>
+          <t>43316</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69333</t>
+          <t>69635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80982</t>
+          <t>81750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14316</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26133</t>
+          <t>27334</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>41138</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49397</t>
+          <t>49645</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41412</t>
+          <t>40744</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51471</t>
+          <t>51030</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85850</t>
+          <t>84649</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98828</t>
+          <t>98310</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22762</t>
+          <t>23575</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38831</t>
+          <t>39259</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20998</t>
+          <t>20483</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37694</t>
+          <t>36250</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47401</t>
+          <t>47646</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69884</t>
+          <t>71043</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>99217</t>
+          <t>98789</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>115286</t>
+          <t>114473</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>105102</t>
+          <t>106546</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>121798</t>
+          <t>122313</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>210960</t>
+          <t>209801</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>233443</t>
+          <t>233198</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,03%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>31735</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48253</t>
+          <t>49672</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>17277</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32376</t>
+          <t>32250</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53365</t>
+          <t>52160</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>76460</t>
+          <t>75580</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>115843</t>
+          <t>114424</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>132757</t>
+          <t>132361</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>137645</t>
+          <t>137771</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>152810</t>
+          <t>152744</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>257657</t>
+          <t>258537</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>280752</t>
+          <t>281957</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>126335</t>
+          <t>126031</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>161135</t>
+          <t>160032</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>101268</t>
+          <t>101381</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>134647</t>
+          <t>136456</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>238919</t>
+          <t>237913</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>285448</t>
+          <t>284186</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>544603</t>
+          <t>545706</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>579403</t>
+          <t>579707</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>608309</t>
+          <t>606500</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>641688</t>
+          <t>641575</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1163246</t>
+          <t>1164508</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1209775</t>
+          <t>1210781</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15408</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>12426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25424</t>
+          <t>25474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43471</t>
+          <t>44059</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>52468</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48007</t>
+          <t>48486</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57932</t>
+          <t>57958</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95362</t>
+          <t>95312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109012</t>
+          <t>108360</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18853</t>
+          <t>19162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32167</t>
+          <t>33253</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24522</t>
+          <t>24565</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34297</t>
+          <t>33896</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>53253</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71780</t>
+          <t>70694</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85094</t>
+          <t>84785</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85061</t>
+          <t>85018</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97033</t>
+          <t>97533</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>161529</t>
+          <t>160277</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179233</t>
+          <t>179634</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22816</t>
+          <t>22864</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18479</t>
+          <t>17929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21697</t>
+          <t>21232</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37177</t>
+          <t>36782</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44015</t>
+          <t>43967</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55824</t>
+          <t>56009</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51426</t>
+          <t>51976</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61730</t>
+          <t>61890</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99559</t>
+          <t>99954</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115039</t>
+          <t>115504</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,47%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15348</t>
+          <t>15075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>28960</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20365</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26880</t>
+          <t>27593</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44974</t>
+          <t>45170</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48288</t>
+          <t>48001</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61613</t>
+          <t>61886</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60819</t>
+          <t>60012</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72447</t>
+          <t>72237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>113171</t>
+          <t>112975</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131265</t>
+          <t>130552</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,55%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10739</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17133</t>
+          <t>16523</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34642</t>
+          <t>34305</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41723</t>
+          <t>41576</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35611</t>
+          <t>35673</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43569</t>
+          <t>43386</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72655</t>
+          <t>73265</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83860</t>
+          <t>83742</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,27%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9520</t>
+          <t>9830</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>11309</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17768</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44753</t>
+          <t>44443</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51799</t>
+          <t>51644</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46861</t>
+          <t>46430</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54989</t>
+          <t>54907</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94244</t>
+          <t>94652</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>105408</t>
+          <t>105195</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22726</t>
+          <t>22898</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20091</t>
+          <t>19536</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35051</t>
+          <t>34693</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47223</t>
+          <t>46373</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69021</t>
+          <t>67791</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>97666</t>
+          <t>97427</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>113291</t>
+          <t>113119</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>107084</t>
+          <t>107442</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>122044</t>
+          <t>122599</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>209131</t>
+          <t>210361</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>230929</t>
+          <t>231779</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34334</t>
+          <t>34289</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51460</t>
+          <t>51306</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24371</t>
+          <t>24257</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41524</t>
+          <t>40661</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62973</t>
+          <t>62311</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>86871</t>
+          <t>87612</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>112716</t>
+          <t>112870</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129842</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>128718</t>
+          <t>129581</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>145871</t>
+          <t>145985</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>247547</t>
+          <t>246806</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>271445</t>
+          <t>272107</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,37%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>136754</t>
+          <t>136692</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>171778</t>
+          <t>172716</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>109816</t>
+          <t>108004</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>142331</t>
+          <t>139898</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>255880</t>
+          <t>255509</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>304123</t>
+          <t>302504</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>531236</t>
+          <t>530298</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>566260</t>
+          <t>566322</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>598222</t>
+          <t>600655</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>630737</t>
+          <t>632549</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1139444</t>
+          <t>1141063</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1187687</t>
+          <t>1188058</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,3%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43204</t>
+          <t>43369</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58463</t>
+          <t>58159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>47503</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61756</t>
+          <t>62020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93703</t>
+          <t>94096</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114510</t>
+          <t>116003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>15123</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17610</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32522</t>
+          <t>31863</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>36645</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58945</t>
+          <t>58552</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20433</t>
+          <t>20119</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83171</t>
+          <t>83955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>10442</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24847</t>
+          <t>24987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35521</t>
+          <t>35451</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122468</t>
+          <t>122329</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,72%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43288</t>
+          <t>42504</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>106026</t>
+          <t>106340</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99802</t>
+          <t>99662</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>114054</t>
+          <t>114207</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128640</t>
+          <t>128779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>215587</t>
+          <t>215657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>11568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46934</t>
+          <t>47038</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54755</t>
+          <t>54633</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>55595</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63008</t>
+          <t>63133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116038</t>
+          <t>116110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15739</t>
+          <t>15428</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44527</t>
+          <t>43285</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>16252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56655</t>
+          <t>62721</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54404</t>
+          <t>54715</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64614</t>
+          <t>64546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33607</t>
+          <t>34849</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71828</t>
+          <t>71502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91623</t>
+          <t>85557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132097</t>
+          <t>132026</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37198</t>
+          <t>37875</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72171</t>
+          <t>71471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12108</t>
+          <t>12170</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>15781</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13684</t>
+          <t>13679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24745</t>
+          <t>24988</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34059</t>
+          <t>33997</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41610</t>
+          <t>41466</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40658</t>
+          <t>40405</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49513</t>
+          <t>49300</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77608</t>
+          <t>77365</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88669</t>
+          <t>88674</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13963</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29872</t>
+          <t>29808</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23641</t>
+          <t>23239</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27602</t>
+          <t>26942</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48220</t>
+          <t>48853</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93505</t>
+          <t>93569</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109414</t>
+          <t>108699</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>131043</t>
+          <t>131445</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>144952</t>
+          <t>144488</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>229842</t>
+          <t>229209</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>250460</t>
+          <t>251120</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19901</t>
+          <t>20758</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>18497</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18761</t>
+          <t>18901</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35053</t>
+          <t>34293</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>111718</t>
+          <t>110861</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>122494</t>
+          <t>122183</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>138396</t>
+          <t>138298</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>149825</t>
+          <t>149504</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>253361</t>
+          <t>254121</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>269653</t>
+          <t>269513</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>125608</t>
+          <t>124635</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>237866</t>
+          <t>229313</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>116013</t>
+          <t>115769</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>169253</t>
+          <t>168429</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>252371</t>
+          <t>251372</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>368345</t>
+          <t>362673</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>425963</t>
+          <t>434516</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>538221</t>
+          <t>539194</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>588444</t>
+          <t>589268</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>641684</t>
+          <t>641928</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1053181</t>
+          <t>1058853</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1169155</t>
+          <t>1170154</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,32%</t>
         </is>
       </c>
     </row>
